--- a/excel/output_stats_vfvv/floyd-warshall/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/floyd-warshall/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>29</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>58</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>13</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>5883500</v>
+        <v>40146700</v>
       </c>
       <c r="K14" t="n">
         <v>108690000</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>30</v>
@@ -1199,10 +1199,10 @@
         <v>0.6</v>
       </c>
       <c r="N16" t="n">
-        <v>350.15</v>
+        <v>333.738</v>
       </c>
       <c r="O16" t="n">
-        <v>350.17</v>
+        <v>349.27</v>
       </c>
     </row>
     <row r="17">
@@ -1210,34 +1210,34 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>1.90119e-09</v>
+        <v>9.223549999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>6.38889e-09</v>
+        <v>14.7672</v>
       </c>
       <c r="E17" t="n">
-        <v>0.297578</v>
+        <v>0.624598</v>
       </c>
       <c r="F17" t="n">
-        <v>1.21465e-17</v>
+        <v>136.206</v>
       </c>
       <c r="G17" t="n">
-        <v>1095650000</v>
+        <v>1754430000</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>25908100000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>24534900000</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>53161800000</v>
       </c>
       <c r="L17" t="n">
         <v>3600000000</v>
@@ -1246,10 +1246,10 @@
         <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>350.151</v>
+        <v>333.737</v>
       </c>
       <c r="O17" t="n">
-        <v>350.21</v>
+        <v>364.1</v>
       </c>
     </row>
     <row r="18">
@@ -1257,34 +1257,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>2.67541e-09</v>
+        <v>1.90119e-09</v>
       </c>
       <c r="D18" t="n">
-        <v>9.166669999999999e-09</v>
+        <v>6.38889e-09</v>
       </c>
       <c r="E18" t="n">
-        <v>0.291863</v>
+        <v>0.297578</v>
       </c>
       <c r="F18" t="n">
-        <v>2.45246e-17</v>
+        <v>1.21465e-17</v>
       </c>
       <c r="G18" t="n">
-        <v>981818000</v>
+        <v>1095650000</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="L18" t="n">
         <v>3600000000</v>
@@ -1293,10 +1293,10 @@
         <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O18" t="n">
-        <v>350.18</v>
+        <v>350.21</v>
       </c>
     </row>
     <row r="19">
@@ -1304,34 +1304,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>4.64603e-10</v>
+        <v>2.67541e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.66667e-09</v>
+        <v>9.166669999999999e-09</v>
       </c>
       <c r="E19" t="n">
-        <v>0.278762</v>
+        <v>0.291863</v>
       </c>
       <c r="F19" t="n">
-        <v>7.74338e-19</v>
+        <v>2.45246e-17</v>
       </c>
       <c r="G19" t="n">
-        <v>600000000</v>
+        <v>981818000</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
         <v>3600000000</v>
@@ -1343,7 +1343,7 @@
         <v>350.15</v>
       </c>
       <c r="O19" t="n">
-        <v>350.17</v>
+        <v>350.18</v>
       </c>
     </row>
     <row r="20">
@@ -1351,7 +1351,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
         <v>4.64603e-10</v>
@@ -1398,34 +1398,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>6.10341e-10</v>
+        <v>4.64603e-10</v>
       </c>
       <c r="D21" t="n">
-        <v>1.94444e-09</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E21" t="n">
-        <v>0.31389</v>
+        <v>0.278762</v>
       </c>
       <c r="F21" t="n">
-        <v>1.18677e-18</v>
+        <v>7.74338e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>1028570000</v>
+        <v>600000000</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>3600000000</v>
@@ -1434,10 +1434,10 @@
         <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O21" t="n">
-        <v>350.18</v>
+        <v>350.17</v>
       </c>
     </row>
     <row r="22">
@@ -1445,7 +1445,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
         <v>6.10341e-10</v>
@@ -1492,34 +1492,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>1.45203e-09</v>
+        <v>6.10341e-10</v>
       </c>
       <c r="D23" t="n">
-        <v>4.72222e-09</v>
+        <v>1.94444e-09</v>
       </c>
       <c r="E23" t="n">
-        <v>0.30749</v>
+        <v>0.31389</v>
       </c>
       <c r="F23" t="n">
-        <v>6.85683e-18</v>
+        <v>1.18677e-18</v>
       </c>
       <c r="G23" t="n">
-        <v>847059000</v>
+        <v>1028570000</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L23" t="n">
         <v>3600000000</v>
@@ -1539,34 +1539,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>1.19266e-10</v>
+        <v>1.45203e-09</v>
       </c>
       <c r="D24" t="n">
-        <v>2.77778e-10</v>
+        <v>4.72222e-09</v>
       </c>
       <c r="E24" t="n">
-        <v>0.429359</v>
+        <v>0.30749</v>
       </c>
       <c r="F24" t="n">
-        <v>3.31295e-20</v>
+        <v>6.85683e-18</v>
       </c>
       <c r="G24" t="n">
-        <v>3600000000</v>
+        <v>847059000</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
         <v>3600000000</v>
@@ -1578,6 +1578,53 @@
         <v>350.151</v>
       </c>
       <c r="O24" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.19266e-10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.77778e-10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.429359</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.31295e-20</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O25" t="n">
         <v>350.23</v>
       </c>
     </row>
